--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo002.xlsx
@@ -8,10 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -98,8 +96,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -407,41 +408,47 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" customWidth="1"/>
-    <col min="6" max="7" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="13.6328125" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -450,24 +457,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo002.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>货币对</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,15 +44,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>数据状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新人</t>
+    <t>错误信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -405,51 +409,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.90625" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" customWidth="1"/>
-    <col min="9" max="9" width="14.08984375" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="18.08984375" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
